--- a/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-origine-effet-indesirable-cisis.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-origine-effet-indesirable-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085851</t>
+    <t>20260911143444</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:51+01:00</t>
+    <t>2026-09-11T14:34:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -143,12 +143,6 @@
   </si>
   <si>
     <t>erreur médicamenteuse</t>
-  </si>
-  <si>
-    <t>16090731000119102</t>
-  </si>
-  <si>
-    <t>exposition professionnelle à un facteur de risque</t>
   </si>
   <si>
     <t>79899007</t>
@@ -495,7 +489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -560,26 +554,18 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-origine-effet-indesirable-cisis.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-origine-effet-indesirable-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260911143444</t>
+    <t>20260916095453</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:34:44+01:00</t>
+    <t>2026-09-16T09:54:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
